--- a/data/trans_orig/Q5414-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q5414-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6318</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>842</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>7340</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>811</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8551</t>
+          <t>7375</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>913</t>
+          <t>912</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8158</t>
+          <t>9122</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>2054</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11029</t>
+          <t>12154</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>281515</t>
+          <t>282432</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>290850</t>
+          <t>290869</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>332995</t>
+          <t>332507</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>341889</t>
+          <t>341898</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>620150</t>
+          <t>619697</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>631668</t>
+          <t>631076</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1122</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9406</t>
+          <t>10500</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9167</t>
+          <t>10254</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2558</t>
+          <t>2535</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11149</t>
+          <t>11682</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>12708</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6036</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19509</t>
+          <t>19120</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>198734</t>
+          <t>198201</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>207325</t>
+          <t>207348</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>316692</t>
+          <t>316383</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>329446</t>
+          <t>329395</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>520173</t>
+          <t>519429</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>535526</t>
+          <t>535348</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7489</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10434</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2261</t>
+          <t>2272</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>12936</t>
+          <t>12712</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15230</t>
+          <t>13797</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15989</t>
+          <t>17290</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9813</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26641</t>
+          <t>25821</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>484991</t>
+          <t>486132</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>496990</t>
+          <t>497134</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>655807</t>
+          <t>654809</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>669677</t>
+          <t>669963</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1145012</t>
+          <t>1145656</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1164796</t>
+          <t>1164511</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -2331,12 +2331,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>970</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8005</t>
+          <t>7918</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2346,12 +2346,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6641</t>
+          <t>6472</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1940</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10750</t>
+          <t>10928</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>960</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9539</t>
+          <t>8578</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>5969</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11210</t>
+          <t>11292</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>297365</t>
+          <t>297157</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>307699</t>
+          <t>307651</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>344430</t>
+          <t>345174</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>353045</t>
+          <t>353010</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>646376</t>
+          <t>646063</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>658797</t>
+          <t>658723</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>8378</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5539</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20341</t>
+          <t>19847</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7773</t>
+          <t>7784</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24228</t>
+          <t>23259</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5066</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21251</t>
+          <t>22927</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12148</t>
+          <t>12033</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30823</t>
+          <t>30031</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>21009</t>
+          <t>20681</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>45516</t>
+          <t>44531</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>224172</t>
+          <t>224568</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>242381</t>
+          <t>242384</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>345389</t>
+          <t>345462</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>368282</t>
+          <t>368223</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>576923</t>
+          <t>579378</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>606229</t>
+          <t>607148</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,04%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2069</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12518</t>
+          <t>12321</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7338</t>
+          <t>7490</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22159</t>
+          <t>22027</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12587</t>
+          <t>12225</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>30510</t>
+          <t>30060</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>7535</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24990</t>
+          <t>25538</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13431</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33545</t>
+          <t>31835</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23757</t>
+          <t>23776</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50461</t>
+          <t>49583</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>528178</t>
+          <t>527851</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>547452</t>
+          <t>547199</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>694417</t>
+          <t>694184</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>718993</t>
+          <t>718532</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1228696</t>
+          <t>1231346</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1260631</t>
+          <t>1262104</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>6297</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6567</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,73%</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11626</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13647</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>327352</t>
+          <t>327444</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>366027</t>
+          <t>366653</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>376718</t>
+          <t>376744</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>698356</t>
+          <t>697531</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>710062</t>
+          <t>710034</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>17854</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3459</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17788</t>
+          <t>18079</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -4498,12 +4498,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12885</t>
+          <t>12765</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>10706</t>
+          <t>10188</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>29376</t>
+          <t>28527</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>15421</t>
+          <t>15671</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>36812</t>
+          <t>35880</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>243057</t>
+          <t>243398</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>252995</t>
+          <t>253099</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>359383</t>
+          <t>359888</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>382453</t>
+          <t>383560</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>609076</t>
+          <t>610880</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>634321</t>
+          <t>634299</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18940</t>
+          <t>19020</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19902</t>
+          <t>18668</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -4954,12 +4954,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4367</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15930</t>
+          <t>15665</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12865</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>33473</t>
+          <t>33711</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20157</t>
+          <t>20554</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42659</t>
+          <t>43067</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -5067,12 +5067,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>574837</t>
+          <t>574420</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>586254</t>
+          <t>586161</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>733540</t>
+          <t>733546</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>757465</t>
+          <t>757487</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1315140</t>
+          <t>1314051</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1340787</t>
+          <t>1341043</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>610</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5557,32 +5557,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1543</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>457</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5592,32 +5592,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>2268</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>610</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5679</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,67%</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>1583</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5381</t>
+          <t>5075</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5670,32 +5670,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2543</t>
+          <t>2737</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>983</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5857</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5705,32 +5705,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4072</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>8539</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -5748,32 +5748,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>366004</t>
+          <t>404887</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>362016</t>
+          <t>400802</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>367532</t>
+          <t>406462</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5783,32 +5783,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>603872</t>
+          <t>434338</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>599575</t>
+          <t>429892</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>607188</t>
+          <t>436539</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5818,32 +5818,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>969877</t>
+          <t>839226</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>965374</t>
+          <t>834372</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>974108</t>
+          <t>842594</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -5861,17 +5861,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5896,17 +5896,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>976124</t>
+          <t>845814</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>976124</t>
+          <t>845814</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>976124</t>
+          <t>845814</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5978,32 +5978,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2147</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>681</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6013,32 +6013,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>6479</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3449</t>
+          <t>3734</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10669</t>
+          <t>10672</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6048,32 +6048,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>8180</t>
+          <t>8592</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12732</t>
+          <t>13333</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -6091,32 +6091,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7686</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13305</t>
+          <t>13592</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6126,32 +6126,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21027</t>
+          <t>22848</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14782</t>
+          <t>16542</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28169</t>
+          <t>31601</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6161,27 +6161,27 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>28713</t>
+          <t>30939</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>21595</t>
+          <t>23296</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>36922</t>
+          <t>40434</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -6204,32 +6204,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>272180</t>
+          <t>299107</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>266634</t>
+          <t>293434</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>275846</t>
+          <t>303151</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6239,32 +6239,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>398771</t>
+          <t>435282</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>390500</t>
+          <t>425673</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>405448</t>
+          <t>442397</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6274,32 +6274,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>670951</t>
+          <t>734388</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>662023</t>
+          <t>723749</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>678726</t>
+          <t>743280</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -6317,17 +6317,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6352,17 +6352,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6387,17 +6387,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>707844</t>
+          <t>773920</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>707844</t>
+          <t>773920</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>707844</t>
+          <t>773920</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6434,32 +6434,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2723</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1053</t>
+          <t>959</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5619</t>
+          <t>5870</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6469,32 +6469,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>8137</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12143</t>
+          <t>12578</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6504,32 +6504,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>10356</t>
+          <t>10861</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5906</t>
+          <t>6794</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15602</t>
+          <t>15925</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,98%</t>
         </is>
       </c>
     </row>
@@ -6547,32 +6547,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9215</t>
+          <t>9674</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14647</t>
+          <t>16012</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6582,32 +6582,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>23569</t>
+          <t>25585</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11771</t>
+          <t>18619</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34088</t>
+          <t>34125</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6617,32 +6617,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>32785</t>
+          <t>35259</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20361</t>
+          <t>27010</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43678</t>
+          <t>45972</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -6660,32 +6660,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>638183</t>
+          <t>703994</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>632311</t>
+          <t>697248</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>642709</t>
+          <t>708509</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6695,32 +6695,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1002644</t>
+          <t>869621</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>990126</t>
+          <t>860507</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1017881</t>
+          <t>877457</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6730,32 +6730,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1640828</t>
+          <t>1573615</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1628340</t>
+          <t>1562182</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1655615</t>
+          <t>1582616</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -6773,17 +6773,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6808,17 +6808,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1033789</t>
+          <t>903343</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1033789</t>
+          <t>903343</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1033789</t>
+          <t>903343</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6843,17 +6843,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1683968</t>
+          <t>1619735</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1683968</t>
+          <t>1619735</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1683968</t>
+          <t>1619735</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
